--- a/apps/be/reports/ImpactCocoa_GMR_Template.xlsx
+++ b/apps/be/reports/ImpactCocoa_GMR_Template.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thinkdataservicesltd.sharepoint.com/sites/ThinkDataServicesIntranet/Shared Documents/SERVICE DELIVERY/PROJECTS/Custom development/AgroEco/ImpactCocoa Database Dev - shared folder/Reporting templates/For review/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://thinkdataservicesltd.sharepoint.com/sites/ThinkDataServicesIntranet/Shared Documents/SERVICE DELIVERY/PROJECTS/Custom development/Think!Data/Think!Cocoa Database Dev - shared folder/Reporting templates/For review/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="16" documentId="11_76217CFF31FAA84381375E740DC4917118F1A5F1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70C7FA2A-F64A-4D7E-86A9-BF50B49EA799}"/>
@@ -88,19 +88,19 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="319">
   <si>
-    <t>ImpactCocoa Data Management Platform</t>
+    <t>Think!Cocoa Data Management Platform</t>
   </si>
   <si>
     <t>Group Member Registry (GMR) – Reporting Template</t>
   </si>
   <si>
-    <t>Rainforest Alliance Annex S13 – Version 1.3  |  Adapted for ImpactCocoa Database</t>
+    <t>Rainforest Alliance Annex S13 – Version 1.3  |  Adapted for Think!Cocoa Database</t>
   </si>
   <si>
     <t>Document Code:</t>
   </si>
   <si>
-    <t>SA-S-SD-14  (ImpactCocoa Edition)</t>
+    <t>SA-S-SD-14  (Think!Cocoa Edition)</t>
   </si>
   <si>
     <t>Version:</t>
@@ -112,7 +112,7 @@
     <t>Applicable to:</t>
   </si>
   <si>
-    <t>AgroEco Ghana – Cooperatives under ImpactCocoa Programme</t>
+    <t>Think!Data – Cooperatives under Think!Cocoa Programme</t>
   </si>
   <si>
     <t>Crop:</t>
@@ -130,7 +130,7 @@
     <t>DB Source:</t>
   </si>
   <si>
-    <t>ImpactCocoa PostgreSQL – farmer_master, plot_master,
+    <t>Think!Cocoa PostgreSQL – farmer_master, plot_master,
 inspection_records, cocoa_purchase</t>
   </si>
   <si>
@@ -146,13 +146,13 @@
     <t>Reporting Year:</t>
   </si>
   <si>
-    <t>⚠  This template is pre-mapped to the ImpactCocoa database schema.  Data must be exported from the ImpactCocoa platform and pasted into tabs 1–3 before submission to the Rainforest Alliance RACP portal.  All coordinates must be in WGS84 / EPSG:4326 decimal-degree format with a minimum of 6 decimal places.</t>
-  </si>
-  <si>
-    <t>ImpactCocoa → Rainforest Alliance GMR  |  Field Mapping Reference</t>
-  </si>
-  <si>
-    <t>This sheet maps every column in the GMR data tabs to the corresponding ImpactCocoa database table and field name.  Use it as the export specification when generating the GMR from the ImpactCocoa platform.</t>
+    <t>⚠  This template is pre-mapped to the Think!Cocoa database schema.  Data must be exported from the Think!Cocoa platform and pasted into tabs 1–3 before submission to the Rainforest Alliance RACP portal.  All coordinates must be in WGS84 / EPSG:4326 decimal-degree format with a minimum of 6 decimal places.</t>
+  </si>
+  <si>
+    <t>Think!Cocoa → Rainforest Alliance GMR  |  Field Mapping Reference</t>
+  </si>
+  <si>
+    <t>This sheet maps every column in the GMR data tabs to the corresponding Think!Cocoa database table and field name.  Use it as the export specification when generating the GMR from the Think!Cocoa platform.</t>
   </si>
   <si>
     <t>GMR Tab</t>
@@ -164,10 +164,10 @@
     <t>GMR Column Name (RA)</t>
   </si>
   <si>
-    <t>ImpactCocoa DB Table</t>
-  </si>
-  <si>
-    <t>ImpactCocoa DB Field</t>
+    <t>Think!Cocoa DB Table</t>
+  </si>
+  <si>
+    <t>Think!Cocoa DB Field</t>
   </si>
   <si>
     <t>Data Type</t>
@@ -320,7 +320,7 @@
     <t>HARDCODE: 1</t>
   </si>
   <si>
-    <t>ImpactCocoa scope = cocoa only. Always 1.</t>
+    <t>Think!Cocoa scope = cocoa only. Always 1.</t>
   </si>
   <si>
     <t>10</t>
@@ -530,7 +530,7 @@
     <t>HARDCODE: 'Cocoa'</t>
   </si>
   <si>
-    <t>Always 'Cocoa' for ImpactCocoa.</t>
+    <t>Always 'Cocoa' for Think!Cocoa.</t>
   </si>
   <si>
     <t>Variety</t>
@@ -611,7 +611,7 @@
     <t>Extract longitude from GPS point. WGS84 DD. Min 6 decimal places. Required for largest plot.</t>
   </si>
   <si>
-    <t>ImpactCocoa – Group Member Registry  |  Tab 1: Farm Information  |  Rainforest Alliance Annex S13 v1.3</t>
+    <t>Think!Cocoa – Group Member Registry  |  Tab 1: Farm Information  |  Rainforest Alliance Annex S13 v1.3</t>
   </si>
   <si>
     <t>FARM</t>
@@ -850,7 +850,7 @@
 (formula)</t>
   </si>
   <si>
-    <t>ImpactCocoa – Group Member Registry  |  Tab 2: Certified Crop &amp; Volumes  |  Rainforest Alliance Annex S13 v1.3</t>
+    <t>Think!Cocoa – Group Member Registry  |  Tab 2: Certified Crop &amp; Volumes  |  Rainforest Alliance Annex S13 v1.3</t>
   </si>
   <si>
     <t>CERTIFIED CROP AND VOLUMES INFORMATION</t>
@@ -957,7 +957,7 @@
     <t>Free text</t>
   </si>
   <si>
-    <t>ImpactCocoa – Group Member Registry  |  Tab 3: Farm Units &amp; GPS Coordinates  |  Rainforest Alliance Annex S13 v1.3</t>
+    <t>Think!Cocoa – Group Member Registry  |  Tab 3: Farm Units &amp; GPS Coordinates  |  Rainforest Alliance Annex S13 v1.3</t>
   </si>
   <si>
     <t>FARM UNIT INFORMATION — WGS84 / EPSG:4326  |  Decimal Degrees  |  Minimum 6 decimal places</t>
@@ -1016,7 +1016,7 @@
 [longitude component]</t>
   </si>
   <si>
-    <t>ImpactCocoa GMR Dashboard – Summary of Group Information</t>
+    <t>Think!Cocoa GMR Dashboard – Summary of Group Information</t>
   </si>
   <si>
     <t>Fill in tabs 1, 2, and 3 first — then review the indicators below. Numbers update automatically when data is entered.</t>
